--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.24031627672675</v>
+        <v>10.2765513949681</v>
       </c>
       <c r="D2" t="n">
-        <v>63.14350963586602</v>
+        <v>10.26082031582823</v>
       </c>
       <c r="E2" t="n">
-        <v>19.19716580607745</v>
+        <v>3.119539443487586</v>
       </c>
       <c r="F2" t="n">
-        <v>19.12716179265735</v>
+        <v>3.108163791306819</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.36022344267447</v>
+        <v>8.183536309434603</v>
       </c>
       <c r="D3" t="n">
-        <v>49.93772195316694</v>
+        <v>8.114879817389628</v>
       </c>
       <c r="E3" t="n">
-        <v>19.19716580607745</v>
+        <v>3.119539443487586</v>
       </c>
       <c r="F3" t="n">
-        <v>19.12716179265735</v>
+        <v>3.108163791306819</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.87899029027783</v>
+        <v>2.417835922170148</v>
       </c>
       <c r="D4" t="n">
-        <v>14.89286872593487</v>
+        <v>2.420091167964417</v>
       </c>
       <c r="E4" t="n">
-        <v>19.19716580607745</v>
+        <v>3.119539443487586</v>
       </c>
       <c r="F4" t="n">
-        <v>19.12716179265735</v>
+        <v>3.108163791306819</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.06072310786557</v>
+        <v>1.959867505028156</v>
       </c>
       <c r="D5" t="n">
-        <v>11.7957489889687</v>
+        <v>1.916809210707414</v>
       </c>
       <c r="E5" t="n">
-        <v>19.19716580607745</v>
+        <v>3.119539443487586</v>
       </c>
       <c r="F5" t="n">
-        <v>19.12716179265735</v>
+        <v>3.108163791306819</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.2533534081715</v>
+        <v>3.453669928827868</v>
       </c>
       <c r="D6" t="n">
-        <v>21.6887593650975</v>
+        <v>3.524423396828344</v>
       </c>
       <c r="E6" t="n">
-        <v>19.19716580607745</v>
+        <v>3.119539443487586</v>
       </c>
       <c r="F6" t="n">
-        <v>19.12716179265735</v>
+        <v>3.108163791306819</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.53211415861669</v>
+        <v>6.261468550775213</v>
       </c>
       <c r="D7" t="n">
-        <v>38.49517629008876</v>
+        <v>6.255466147139424</v>
       </c>
       <c r="E7" t="n">
-        <v>19.19716580607745</v>
+        <v>3.119539443487586</v>
       </c>
       <c r="F7" t="n">
-        <v>19.12716179265735</v>
+        <v>3.108163791306819</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>55.76868845869044</v>
+        <v>9.062411874537197</v>
       </c>
       <c r="D8" t="n">
-        <v>55.73467199938619</v>
+        <v>9.056884199900257</v>
       </c>
       <c r="E8" t="n">
-        <v>19.19716580607745</v>
+        <v>3.119539443487586</v>
       </c>
       <c r="F8" t="n">
-        <v>19.12716179265735</v>
+        <v>3.108163791306819</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
